--- a/ElectrekTestPlan.xlsx
+++ b/ElectrekTestPlan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t xml:space="preserve">ELECTREK TEST PLAN</t>
   </si>
@@ -107,6 +107,51 @@
   </si>
   <si>
     <t xml:space="preserve">click on map to get lat long, enter lat long as election bookmark, make territory England</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adminmode voronio layers(admin mode decide rlevels, which decides area(div/ward) and Field(PD/Walk) type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose Canvasscards area layer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">click Fields(not STAT)  at Area layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD voronoi layers appear with option to print</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose  VIApp at area layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">click Fields(not STAT) at Area layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD voronoi layer appears with option to export html to static website url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonAdminmode voronio layers(admin mode decide rlevels, which decides area(div/ward) and Field(PD/Walk) type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk voronoi layer appears with option to print</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk voronoi layer appears with option to export html to static website url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CanvassCard data entry, data export/import/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Web App data entry export/import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregate and Track VI data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendar functions for resource actitivity planning and target tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanban functions for area activity planning and tracking.</t>
   </si>
 </sst>
 </file>
@@ -324,12 +369,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -483,6 +528,97 @@
       </c>
       <c r="B17" s="1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ElectrekTestPlan.xlsx
+++ b/ElectrekTestPlan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t xml:space="preserve">ELECTREK TEST PLAN</t>
   </si>
@@ -137,6 +137,18 @@
   </si>
   <si>
     <t xml:space="preserve">Walk voronoi layer appears with option to export html to static website url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canvasscards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choose streets to enter data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">click streets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">street name nodes displayed and readable </t>
   </si>
   <si>
     <t xml:space="preserve">CanvassCard data entry, data export/import/</t>
@@ -166,7 +178,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -188,7 +199,6 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -369,7 +379,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.9"/>
@@ -559,7 +569,7 @@
       <c r="C21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -592,7 +602,7 @@
       <c r="C24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -600,25 +610,45 @@
       <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="D25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
